--- a/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01161410101534100</v>
+        <v>01161410101534107</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,92 @@
         <v>7</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>797_大菊黄_undefined_undefined_5stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>798_大菊粉_undefined_undefined_5stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>526_大刺秦_Eryngium_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>790_铁线莲粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" t="str">
+        <v>327_文竹_asparagus fern_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>341_南天竹绿_undefined_Nandina domestica Thunb._1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>554_伊朗红柳（进口）_iran red willow_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>768_清香木_undefined_undefined_undefinedundefined</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01161410101534107</v>
+        <v>0116141010153410710105554155100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
@@ -606,6 +606,9 @@
       <c r="C21" t="str">
         <v>768_清香木_undefined_undefined_undefinedundefined</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -664,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0116141010153410710105554155100</v>
+        <v>0116141010153410710105554155105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -610,9 +610,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>329_柔丝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>449_柔丽思 绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>118_绣球老绿_Hydrangea Garden Lace_Hydrangea L._1stem</v>
+      </c>
+      <c r="F24" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F25" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>127_绣球孔雀粉_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F26" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F27" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>546_非洲菊绿宝石_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>5</v>
+      </c>
+      <c r="C30" t="str">
+        <v>844_荚米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>435_猫眼_Echinacea_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -667,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0116141010153410710105554155105</v>
+        <v>01161410101534107101055541551051053020203051050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
@@ -689,6 +689,9 @@
       <c r="C31" t="str">
         <v>435_猫眼_Echinacea_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -747,7 +750,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01161410101534107101055541551051053020203051050</v>
+        <v>011614101015341071010555415510510530202030510510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -693,9 +693,92 @@
         <v>10</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>501_姜荷花 绿_Curcuma green_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>409_姜荷花 红_Curcuma red_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>6</v>
+      </c>
+      <c r="C36" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F41" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -750,7 +833,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>011614101015341071010555415510510530202030510510</v>
+        <v>01161410101534107101055541551051053020203051051055557131312151</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
@@ -773,7 +773,7 @@
         <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
       </c>
       <c r="F41" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +833,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01161410101534107101055541551051053020203051051055557131312151</v>
+        <v>011614101015341071010555415510510530202030510510555571313121510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-18.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -776,9 +776,178 @@
         <v>10</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>7</v>
+      </c>
+      <c r="C42" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F42" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>18_波浪黄洋桔梗_Wavy Yellow Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F46" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>7_翠绿洋桔梗_Dark Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="C48" t="str" xml:space="preserve">
+        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F49" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>8</v>
+      </c>
+      <c r="C51" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F51" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>792_珍珠梅白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>9</v>
+      </c>
+      <c r="C53" t="str">
+        <v>771_美洲茶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>398_小香球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>10</v>
+      </c>
+      <c r="C56" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str">
+        <v>11</v>
+      </c>
+      <c r="C57" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>432_小刺秦/情人果_small Eryngium_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>453_国产菠萝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>788_国产直葱白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L60"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -833,7 +1002,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>011614101015341071010555415510510530202030510510555571313121510</v>
+        <v>011614101015341071010555415510510530202030510510555571313121510151051015551510451010549203010510</v>
       </c>
     </row>
   </sheetData>
